--- a/data/trans_dic/P68-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P68-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensan que su trabajo les afecta negativamente</t>
+          <t>Población que piensan que su trabajo les afecta negativamente (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,83; 33,86</t>
+          <t>19,76; 32,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 21,52</t>
+          <t>6,74; 21,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,75; 33,5</t>
+          <t>13,38; 33,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,8; 22,03</t>
+          <t>1,84; 19,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,13; 20,28</t>
+          <t>9,4; 20,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 19,55</t>
+          <t>5,86; 19,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,49; 19,74</t>
+          <t>7,36; 21,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 33,86</t>
+          <t>9,75; 32,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,52; 25,37</t>
+          <t>17,01; 25,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 17,73</t>
+          <t>7,8; 17,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,86; 23,1</t>
+          <t>11,8; 23,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 22,04</t>
+          <t>7,33; 21,22</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,7; 29,28</t>
+          <t>21,54; 29,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,44; 27,14</t>
+          <t>18,95; 27,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,39; 28,49</t>
+          <t>19,28; 28,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,37; 22,95</t>
+          <t>12,65; 23,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,02; 28,87</t>
+          <t>18,55; 27,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,94; 30,2</t>
+          <t>19,27; 29,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,66; 21,6</t>
+          <t>12,85; 21,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 19,67</t>
+          <t>7,44; 20,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,92; 27,89</t>
+          <t>21,79; 27,71</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19,89; 26,8</t>
+          <t>20,0; 26,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,8; 23,95</t>
+          <t>17,67; 24,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 19,7</t>
+          <t>11,04; 19,73</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,79; 26,07</t>
+          <t>19,44; 26,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,6; 27,63</t>
+          <t>19,35; 27,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,93; 29,03</t>
+          <t>20,79; 29,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,25; 24,62</t>
+          <t>17,44; 25,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,77; 28,32</t>
+          <t>18,27; 28,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,56; 30,91</t>
+          <t>20,66; 31,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,31; 28,22</t>
+          <t>18,3; 27,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 25,4</t>
+          <t>18,17; 25,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,86; 25,57</t>
+          <t>19,74; 25,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,88; 27,52</t>
+          <t>21,28; 27,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,82; 27,09</t>
+          <t>20,71; 27,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,77; 24,06</t>
+          <t>18,63; 24,11</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,44; 30,53</t>
+          <t>21,6; 30,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,26; 30,32</t>
+          <t>19,91; 29,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,12; 29,85</t>
+          <t>20,43; 30,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 22,84</t>
+          <t>5,5; 22,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,26; 28,64</t>
+          <t>16,63; 28,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,24; 23,99</t>
+          <t>13,18; 24,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,75; 29,38</t>
+          <t>18,44; 29,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,09; 50,83</t>
+          <t>27,94; 50,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,09; 28,39</t>
+          <t>21,19; 28,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19,04; 26,15</t>
+          <t>18,94; 26,33</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,8; 28,02</t>
+          <t>20,56; 28,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,67; 29,51</t>
+          <t>11,44; 30,02</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,13; 35,87</t>
+          <t>21,37; 34,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,23; 34,75</t>
+          <t>21,71; 35,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,05; 34,22</t>
+          <t>19,83; 34,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,07; 27,28</t>
+          <t>18,33; 27,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,61; 32,86</t>
+          <t>12,74; 33,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,22; 46,99</t>
+          <t>23,25; 47,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,18; 40,13</t>
+          <t>21,17; 39,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,32; 31,76</t>
+          <t>22,66; 32,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20,53; 32,17</t>
+          <t>21,06; 32,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,44; 36,49</t>
+          <t>24,62; 36,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,69; 34,41</t>
+          <t>22,75; 34,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,36; 27,76</t>
+          <t>21,46; 28,22</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,17; 35,42</t>
+          <t>6,63; 39,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,63; 30,74</t>
+          <t>7,66; 32,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,68</t>
+          <t>0,0; 48,75</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,98; 28,8</t>
+          <t>8,8; 28,56</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,82; 26,77</t>
+          <t>22,95; 26,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,2; 25,66</t>
+          <t>21,21; 25,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,58; 27,28</t>
+          <t>22,46; 27,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,41; 20,79</t>
+          <t>11,41; 20,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,17; 24,41</t>
+          <t>19,23; 24,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,07; 25,82</t>
+          <t>20,11; 25,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,57; 23,82</t>
+          <t>18,4; 23,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,89; 30,1</t>
+          <t>20,51; 29,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,11; 25,31</t>
+          <t>22,16; 25,42</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21,42; 24,82</t>
+          <t>21,41; 24,97</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,5; 25,1</t>
+          <t>21,42; 24,84</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,16; 23,17</t>
+          <t>16,16; 23,37</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensan que su trabajo les afecta negativamente</t>
+          <t>Población que piensan que su trabajo les afecta negativamente (tasa de respuesta: 99,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35016; 59789</t>
+          <t>34898; 58085</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5735; 17616</t>
+          <t>5516; 17644</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10728; 26136</t>
+          <t>10438; 25920</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1514; 18523</t>
+          <t>1544; 15996</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12878; 28623</t>
+          <t>13269; 29042</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5093; 17161</t>
+          <t>5142; 17430</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5961; 18134</t>
+          <t>6759; 19452</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8052; 26908</t>
+          <t>7751; 26196</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52473; 80612</t>
+          <t>54027; 81510</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12805; 30084</t>
+          <t>13241; 29050</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20148; 39245</t>
+          <t>20051; 39484</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12330; 36049</t>
+          <t>11995; 34701</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>120739; 162859</t>
+          <t>119845; 163752</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70740; 104135</t>
+          <t>72713; 104742</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66359; 97467</t>
+          <t>65969; 98350</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>42543; 78946</t>
+          <t>43493; 80021</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64470; 97834</t>
+          <t>62872; 94194</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52514; 83721</t>
+          <t>53410; 82708</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34658; 59121</t>
+          <t>35162; 59655</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25940; 68083</t>
+          <t>25758; 69910</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>196259; 249658</t>
+          <t>195025; 248051</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131448; 177134</t>
+          <t>132156; 177279</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>109610; 147532</t>
+          <t>108840; 150404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>73534; 135916</t>
+          <t>76216; 136132</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>105262; 146058</t>
+          <t>108902; 146952</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83534; 117734</t>
+          <t>82441; 118101</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95653; 132630</t>
+          <t>94989; 133320</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>78807; 112500</t>
+          <t>79707; 114597</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>57179; 86261</t>
+          <t>55642; 85650</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58540; 88015</t>
+          <t>58835; 89495</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57768; 89049</t>
+          <t>57753; 87813</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63290; 88174</t>
+          <t>63065; 89155</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>171774; 221071</t>
+          <t>170742; 220081</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>148452; 195632</t>
+          <t>151317; 198047</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160867; 209290</t>
+          <t>159950; 210081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>150946; 193417</t>
+          <t>149793; 193882</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>92670; 131940</t>
+          <t>93338; 132079</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74283; 111163</t>
+          <t>72989; 108450</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73170; 108531</t>
+          <t>74299; 109318</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41647; 169420</t>
+          <t>40787; 169961</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27489; 48402</t>
+          <t>28101; 48376</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29967; 54326</t>
+          <t>29837; 55037</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42973; 71139</t>
+          <t>44646; 71471</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>126062; 228126</t>
+          <t>125381; 225947</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>126776; 170691</t>
+          <t>127422; 171956</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>112937; 155072</t>
+          <t>112338; 156150</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>126011; 169706</t>
+          <t>124548; 170304</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>138976; 351234</t>
+          <t>136236; 357358</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34479; 58515</t>
+          <t>34869; 57022</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33407; 54683</t>
+          <t>34157; 55951</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32801; 55993</t>
+          <t>32450; 57109</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53454; 80695</t>
+          <t>54214; 82290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8109; 21126</t>
+          <t>8189; 21703</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16185; 32744</t>
+          <t>16204; 32920</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21950; 41592</t>
+          <t>21940; 41137</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45995; 65443</t>
+          <t>46698; 66396</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>46689; 73161</t>
+          <t>47905; 73797</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55496; 82848</t>
+          <t>55898; 83486</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60630; 91969</t>
+          <t>60808; 91738</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>107213; 139315</t>
+          <t>107691; 141644</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1462</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 1339</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3123,47 +3123,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>877; 6002</t>
+          <t>1124; 6647</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1313</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 1260</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 1587</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1177; 5456</t>
+          <t>1359; 5688</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 1635</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 1546</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5884</t>
+          <t>0; 5061</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3114; 9992</t>
+          <t>3053; 9909</t>
         </is>
       </c>
     </row>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 613</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 613</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0; 910</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>432161; 506905</t>
+          <t>434510; 510003</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>300778; 363978</t>
+          <t>300958; 365159</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>318451; 384700</t>
+          <t>316701; 384864</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>221407; 403545</t>
+          <t>221500; 403377</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>195809; 249326</t>
+          <t>196389; 247541</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>190384; 244971</t>
+          <t>190759; 242807</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>191645; 245787</t>
+          <t>189877; 242026</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>301871; 435034</t>
+          <t>296499; 430214</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>644460; 737682</t>
+          <t>646055; 740870</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>506992; 587553</t>
+          <t>506861; 591211</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>525085; 613144</t>
+          <t>523190; 606579</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>547345; 784691</t>
+          <t>547157; 791217</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P68-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P68-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,76; 32,9</t>
+          <t>20,18; 33,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,74; 21,55</t>
+          <t>6,46; 22,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,38; 33,22</t>
+          <t>13,51; 32,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 19,03</t>
+          <t>2,95; 23,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 20,58</t>
+          <t>9,23; 20,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 19,85</t>
+          <t>5,86; 19,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 21,18</t>
+          <t>6,67; 20,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 32,96</t>
+          <t>8,95; 30,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,01; 25,66</t>
+          <t>16,22; 25,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 17,12</t>
+          <t>7,82; 17,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,8; 23,24</t>
+          <t>11,57; 23,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 21,22</t>
+          <t>7,38; 21,48</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,54; 29,44</t>
+          <t>21,94; 29,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,95; 27,3</t>
+          <t>18,51; 27,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19,28; 28,74</t>
+          <t>19,43; 29,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,65; 23,27</t>
+          <t>12,7; 23,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,55; 27,8</t>
+          <t>18,88; 27,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,27; 29,84</t>
+          <t>19,19; 29,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,85; 21,79</t>
+          <t>12,8; 21,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 20,2</t>
+          <t>12,15; 20,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,79; 27,71</t>
+          <t>22,05; 27,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20,0; 26,83</t>
+          <t>20,03; 26,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,67; 24,42</t>
+          <t>17,75; 24,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,04; 19,73</t>
+          <t>13,94; 20,96</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,44; 26,23</t>
+          <t>19,09; 26,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19,35; 27,71</t>
+          <t>19,51; 27,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,79; 29,18</t>
+          <t>20,39; 28,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,44; 25,08</t>
+          <t>17,12; 24,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,27; 28,12</t>
+          <t>18,38; 28,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,66; 31,43</t>
+          <t>20,78; 31,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 27,83</t>
+          <t>17,9; 27,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,17; 25,68</t>
+          <t>18,54; 25,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,74; 25,45</t>
+          <t>20,05; 25,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,28; 27,86</t>
+          <t>21,09; 27,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20,71; 27,2</t>
+          <t>20,83; 27,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,63; 24,11</t>
+          <t>18,65; 23,92</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,6; 30,56</t>
+          <t>21,2; 30,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,91; 29,58</t>
+          <t>20,56; 30,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,43; 30,06</t>
+          <t>20,45; 29,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 22,92</t>
+          <t>18,76; 26,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>16,63; 28,62</t>
+          <t>16,0; 28,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,18; 24,31</t>
+          <t>13,49; 24,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,44; 29,52</t>
+          <t>17,42; 29,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,94; 50,35</t>
+          <t>25,22; 31,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,19; 28,6</t>
+          <t>21,32; 28,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,94; 26,33</t>
+          <t>18,98; 26,16</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,56; 28,12</t>
+          <t>20,84; 28,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,44; 30,02</t>
+          <t>22,56; 27,48</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,37; 34,95</t>
+          <t>21,55; 35,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,71; 35,56</t>
+          <t>21,37; 35,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,83; 34,9</t>
+          <t>20,32; 35,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,33; 27,82</t>
+          <t>18,12; 26,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,74; 33,76</t>
+          <t>12,09; 32,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,25; 47,24</t>
+          <t>23,36; 46,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,17; 39,69</t>
+          <t>20,69; 40,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,66; 32,22</t>
+          <t>22,59; 31,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,06; 32,45</t>
+          <t>20,83; 32,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,62; 36,77</t>
+          <t>24,96; 36,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22,75; 34,33</t>
+          <t>22,37; 34,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,46; 28,22</t>
+          <t>20,94; 27,53</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,64</t>
+          <t>0,0; 78,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,63; 39,23</t>
+          <t>7,3; 40,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,66; 32,04</t>
+          <t>6,85; 30,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,75</t>
+          <t>0,0; 47,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,8; 28,56</t>
+          <t>9,2; 28,66</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>22,95; 26,94</t>
+          <t>22,72; 26,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21,21; 25,74</t>
+          <t>21,07; 25,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,46; 27,29</t>
+          <t>22,39; 27,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,41; 20,78</t>
+          <t>18,15; 22,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,23; 24,23</t>
+          <t>18,7; 24,18</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,11; 25,59</t>
+          <t>20,1; 25,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,4; 23,45</t>
+          <t>18,53; 23,46</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,51; 29,77</t>
+          <t>21,32; 25,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>22,16; 25,42</t>
+          <t>22,24; 25,33</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21,41; 24,97</t>
+          <t>21,35; 24,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21,42; 24,84</t>
+          <t>21,43; 24,9</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,16; 23,37</t>
+          <t>20,0; 22,99</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>15899</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>25117</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34898; 58085</t>
+          <t>35634; 58917</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5516; 17644</t>
+          <t>5289; 18191</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10438; 25920</t>
+          <t>10537; 25483</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1544; 15996</t>
+          <t>2916; 22831</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13269; 29042</t>
+          <t>13021; 28540</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5142; 17430</t>
+          <t>5146; 17515</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6759; 19452</t>
+          <t>6124; 19276</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7751; 26196</t>
+          <t>8047; 27807</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54027; 81510</t>
+          <t>51527; 81102</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13241; 29050</t>
+          <t>13262; 30106</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20051; 39484</t>
+          <t>19654; 40376</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11995; 34701</t>
+          <t>13924; 40532</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59074</t>
+          <t>69593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49949</t>
+          <t>51512</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>109022</t>
+          <t>121105</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>119845; 163752</t>
+          <t>122059; 163259</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72713; 104742</t>
+          <t>71029; 104689</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65969; 98350</t>
+          <t>66472; 100529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43493; 80021</t>
+          <t>49479; 91631</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62872; 94194</t>
+          <t>63981; 94852</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53410; 82708</t>
+          <t>53189; 82213</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>35162; 59655</t>
+          <t>35037; 59504</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25758; 69910</t>
+          <t>37943; 65033</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>195025; 248051</t>
+          <t>197418; 249017</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>132156; 177279</t>
+          <t>132377; 177515</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>108840; 150404</t>
+          <t>109348; 150898</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76216; 136132</t>
+          <t>97903; 147136</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95531</t>
+          <t>109977</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>75552</t>
+          <t>86641</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>171084</t>
+          <t>196618</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>108902; 146952</t>
+          <t>106920; 147363</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82441; 118101</t>
+          <t>83156; 117392</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94989; 133320</t>
+          <t>93165; 131005</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79707; 114597</t>
+          <t>91276; 130605</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55642; 85650</t>
+          <t>55971; 86806</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58835; 89495</t>
+          <t>59175; 88985</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57753; 87813</t>
+          <t>56489; 85674</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>63065; 89155</t>
+          <t>72817; 101766</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>170742; 220081</t>
+          <t>173379; 222412</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>151317; 198047</t>
+          <t>149919; 194221</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>159950; 210081</t>
+          <t>160908; 211961</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>149793; 193882</t>
+          <t>172724; 221566</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>108553</t>
+          <t>120530</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>154949</t>
+          <t>126515</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>263502</t>
+          <t>247045</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93338; 132079</t>
+          <t>91628; 130230</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72989; 108450</t>
+          <t>75363; 111809</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>74299; 109318</t>
+          <t>74346; 108291</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40787; 169961</t>
+          <t>101254; 141606</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28101; 48376</t>
+          <t>27036; 48659</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29837; 55037</t>
+          <t>30552; 55670</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44646; 71471</t>
+          <t>42182; 70973</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>125381; 225947</t>
+          <t>113134; 141889</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>127422; 171956</t>
+          <t>128161; 173188</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>112338; 156150</t>
+          <t>112565; 155146</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124548; 170304</t>
+          <t>126230; 170247</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>136236; 357358</t>
+          <t>222966; 271635</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67436</t>
+          <t>72023</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>55507</t>
+          <t>61768</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>122943</t>
+          <t>133791</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34869; 57022</t>
+          <t>35161; 57497</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34157; 55951</t>
+          <t>33632; 55734</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32450; 57109</t>
+          <t>33250; 57943</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54214; 82290</t>
+          <t>58730; 86824</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8189; 21703</t>
+          <t>7773; 20762</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16204; 32920</t>
+          <t>16281; 32565</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21940; 41137</t>
+          <t>21440; 41705</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>46698; 66396</t>
+          <t>52180; 72198</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>47905; 73797</t>
+          <t>47379; 73400</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55898; 83486</t>
+          <t>56670; 83565</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60808; 91738</t>
+          <t>59792; 91470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>107691; 141644</t>
+          <t>116235; 152820</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>6667</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1124; 6647</t>
+          <t>1400; 7694</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1359; 5688</t>
+          <t>1352; 6079</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5061</t>
+          <t>0; 4964</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3053; 9909</t>
+          <t>3579; 11143</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>339505</t>
+          <t>385010</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>354215</t>
+          <t>345334</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>693720</t>
+          <t>730344</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>434510; 510003</t>
+          <t>430098; 508849</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>300958; 365159</t>
+          <t>298880; 363016</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>316701; 384864</t>
+          <t>315797; 384409</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>221500; 403377</t>
+          <t>345993; 427477</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>196389; 247541</t>
+          <t>190991; 247029</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>190759; 242807</t>
+          <t>190709; 245637</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>189877; 242026</t>
+          <t>191223; 242145</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>296499; 430214</t>
+          <t>318644; 374504</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>646055; 740870</t>
+          <t>648329; 738299</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>506861; 591211</t>
+          <t>505548; 585496</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>523190; 606579</t>
+          <t>523285; 608126</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>547157; 791217</t>
+          <t>680340; 782010</t>
         </is>
       </c>
     </row>
